--- a/CHH_SOP update.xlsx
+++ b/CHH_SOP update.xlsx
@@ -744,6 +744,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1" s="7">
       <c r="A4" s="13" t="inlineStr">
         <is>
@@ -840,11 +841,11 @@
       </c>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t>1) เซลส์ส่งฟอร์ม + เอกสาร
+          <t>1) เซลล์ส่งฟอร์ม + เอกสาร
 2) บัญชีตรวจครบถ้วน
 3) บัญชีสร้างรหัสใน D365
 4) ตั้ง Payment Term / Billing cycle
-5) แอดมินยืนยันรหัสกลับเซลส์</t>
+5) แอดมินยืนยันรหัสกลับเซลล์</t>
         </is>
       </c>
       <c r="G6" s="17" t="inlineStr">
@@ -909,7 +910,7 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>บัญชี / เซลส์</t>
+          <t>บัญชี / เซลล์</t>
         </is>
       </c>
       <c r="I7" s="19" t="inlineStr">
@@ -1134,7 +1135,7 @@
       </c>
       <c r="F12" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์รับเรื่อง
+          <t>1) เซลล์รับเรื่อง
 2) ลงทะเบียน Lead/Inquiry
 3) ส่งฟอร์มมาตรฐานให้ลูกค้ากรอก
 4) เปิด Inquiry No.</t>
@@ -1147,7 +1148,7 @@
       </c>
       <c r="H12" s="21" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I12" s="21" t="inlineStr">
@@ -1189,7 +1190,7 @@
       </c>
       <c r="F13" s="17" t="inlineStr">
         <is>
-          <t>1) เซลส์ทบทวน checklist
+          <t>1) เซลล์ทบทวน checklist
 2) ระบุข้อขาด
 3) กลับไปขอลูกค้า หรือ Assume + ระบุชัดเจน
 4) ปิด DOR</t>
@@ -1202,12 +1203,12 @@
       </c>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I13" s="17" t="inlineStr">
         <is>
-          <t>หัวหน้าเซลส์ (กรณี Assume)</t>
+          <t>หัวหน้าเซลล์ (กรณี Assume)</t>
         </is>
       </c>
       <c r="J13" s="17" t="inlineStr">
@@ -1245,9 +1246,9 @@
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t>1) นัดวัน
-2) ทีมเทคนิค + เซลส์ลง site
+2) ทีมเทคนิค + เซลล์ลง site
 3) วัด+ถ่ายรูป+กรอกฟอร์ม
-4) อัพโหลดเข้า Folder งาน</t>
+4) อัปโหลดเข้า Folder งาน</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr">
@@ -1257,7 +1258,7 @@
       </c>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t>เซลส์เทคนิค / ฝ่ายติดตั้ง</t>
+          <t>เซลล์เทคนิค / ฝ่ายติดตั้ง</t>
         </is>
       </c>
       <c r="I14" s="21" t="inlineStr">
@@ -1532,7 +1533,7 @@
       </c>
       <c r="H19" s="19" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I19" s="19" t="inlineStr">
@@ -1574,7 +1575,7 @@
       </c>
       <c r="F20" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์รับคำขอ
+          <t>1) เซลล์รับคำขอ
 2) ขออนุมัติส่วนลดตาม Authority
 3) ส่ง QT Revised
 4) บันทึกเหตุผล</t>
@@ -1587,7 +1588,7 @@
       </c>
       <c r="H20" s="21" t="inlineStr">
         <is>
-          <t>เซลส์ + ฝ่ายประเมิน</t>
+          <t>เซลล์ + ฝ่ายประเมิน</t>
         </is>
       </c>
       <c r="I20" s="21" t="inlineStr">
@@ -1641,12 +1642,12 @@
       </c>
       <c r="H21" s="19" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I21" s="19" t="inlineStr">
         <is>
-          <t>หัวหน้าเซลส์</t>
+          <t>หัวหน้าเซลล์</t>
         </is>
       </c>
       <c r="J21" s="19" t="inlineStr">
@@ -1699,7 +1700,7 @@
       </c>
       <c r="F23" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์ส่ง Drawing Request
+          <t>1) เซลล์ส่ง Drawing Request
 2) ฝ่ายแบบรับ + ตรวจครบ
 3) ลงทะเบียน Drawing Job + Schedule</t>
         </is>
@@ -1864,7 +1865,7 @@
       <c r="F26" s="19" t="inlineStr">
         <is>
           <t>1) นัดประชุม
-2) ฝ่ายแบบ+เซลส์ร่วม
+2) ฝ่ายแบบ+เซลล์ร่วม
 3) บันทึก MoM (Minutes of Meeting)
 4) แก้แบบตามที่ตกลง</t>
         </is>
@@ -1876,7 +1877,7 @@
       </c>
       <c r="H26" s="19" t="inlineStr">
         <is>
-          <t>ฝ่ายแบบ + เซลส์</t>
+          <t>ฝ่ายแบบ + เซลล์</t>
         </is>
       </c>
       <c r="I26" s="19" t="inlineStr">
@@ -1886,7 +1887,7 @@
       </c>
       <c r="J26" s="19" t="inlineStr">
         <is>
-          <t>เซลส์ต้องร่วมเสมอ / โครงการใหญ่ต้อง Kick-off Meeting / ห้ามฝ่ายแบบรับ-ตกลงเปลี่ยนเอง</t>
+          <t>เซลล์ต้องร่วมเสมอ / โครงการใหญ่ต้อง Kick-off Meeting / ห้ามฝ่ายแบบรับ-ตกลงเปลี่ยนเอง</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1919,7 @@
       </c>
       <c r="F27" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์ส่งแบบให้ลูกค้า
+          <t>1) เซลล์ส่งแบบให้ลูกค้า
 2) แจ้งกฎ Free 3 revisions
 3) ติดตามผลทุก 2 วัน</t>
         </is>
@@ -1930,7 +1931,7 @@
       </c>
       <c r="H27" s="21" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I27" s="21" t="inlineStr">
@@ -1995,7 +1996,7 @@
       </c>
       <c r="J28" s="19" t="inlineStr">
         <is>
-          <t>เกิน 3 รอบ → Charge ต่อรอบ + เซลส์ทำเอกสารเก็บเงินเพิ่ม</t>
+          <t>เกิน 3 รอบ → Charge ต่อรอบ + เซลล์ทำเอกสารเก็บเงินเพิ่ม</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2030,7 @@
         <is>
           <t>1) รับเอกสาร
 2) Stamp "AFC"
-3) อัพโหลดเข้า Folder + Lock
+3) อัปโหลดเข้า Folder + Lock
 4) แจ้งทุกฝ่าย</t>
         </is>
       </c>
@@ -2082,7 +2083,7 @@
       </c>
       <c r="F30" s="19" t="inlineStr">
         <is>
-          <t>1) เซลส์รับ
+          <t>1) เซลล์รับ
 2) แอดมินรับเอกสาร
 3) Scan + เก็บ
 4) ตรวจครบถ้วนเบื้องต้น</t>
@@ -2138,7 +2139,7 @@
       <c r="F31" s="17" t="inlineStr">
         <is>
           <t>1) Cross-check ทีละข้อ
-2) ถ้าไม่ตรง → แจ้งเซลส์แก้กับลูกค้า
+2) ถ้าไม่ตรง → แจ้งเซลล์แก้กับลูกค้า
 3) Sign-off ก่อนเปิด SO</t>
         </is>
       </c>
@@ -2154,7 +2155,7 @@
       </c>
       <c r="I31" s="17" t="inlineStr">
         <is>
-          <t>หัวหน้าแอดมิน + เซลส์</t>
+          <t>หัวหน้าแอดมิน + เซลล์</t>
         </is>
       </c>
       <c r="J31" s="17" t="inlineStr">
@@ -2247,7 +2248,7 @@
       <c r="F33" s="21" t="inlineStr">
         <is>
           <t>1) บัญชีออกใบเรียกเก็บมัดจำ
-2) เซลส์ส่งลูกค้า
+2) เซลล์ส่งลูกค้า
 3) ติดตามทุก 2 วัน</t>
         </is>
       </c>
@@ -2258,7 +2259,7 @@
       </c>
       <c r="H33" s="21" t="inlineStr">
         <is>
-          <t>บัญชี AR + เซลส์</t>
+          <t>บัญชี AR + เซลล์</t>
         </is>
       </c>
       <c r="I33" s="21" t="inlineStr">
@@ -2354,7 +2355,7 @@
       </c>
       <c r="F35" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์ขออนุมัติ
+          <t>1) เซลล์ขออนุมัติ
 2) ผู้บริหารพิจารณา
 3) บันทึกเอกสาร + แผนเก็บตามภายหลัง
 4) ติดตามรายสัปดาห์</t>
@@ -2367,7 +2368,7 @@
       </c>
       <c r="H35" s="21" t="inlineStr">
         <is>
-          <t>เซลส์ + แอดมิน</t>
+          <t>เซลล์ + แอดมิน</t>
         </is>
       </c>
       <c r="I35" s="21" t="inlineStr">
@@ -2755,8 +2756,8 @@
       </c>
       <c r="F43" s="19" t="inlineStr">
         <is>
-          <t>1) Planner แจ้งเซลส์
-2) เซลส์แจ้งลูกค้า
+          <t>1) Planner แจ้งเซลล์
+2) เซลล์แจ้งลูกค้า
 3) ปรับ SO Delivery Date ใน ERP
 4) บันทึก Confirmation</t>
         </is>
@@ -2768,7 +2769,7 @@
       </c>
       <c r="H43" s="19" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I43" s="19" t="inlineStr">
@@ -4000,7 +4001,7 @@
           <t>1) เปิด ECO
 2) ประเมินผลกระทบ
 3) ลูกค้าอนุมัติ + จ่ายเพิ่ม
-4) อัพแบบ + แจ้งทุก station
+4) อัปแบบ + แจ้งทุก station
 5) เคลียร์ WIP เก่า</t>
         </is>
       </c>
@@ -4470,8 +4471,8 @@
       <c r="F77" s="21" t="inlineStr">
         <is>
           <t>1) Planner update SO Status = RTS
-2) แจ้งเซลส์ทันที
-3) เซลส์ติดต่อลูกค้านัดวันส่ง</t>
+2) แจ้งเซลล์ทันที
+3) เซลล์ติดต่อลูกค้านัดวันส่ง</t>
         </is>
       </c>
       <c r="G77" s="21" t="inlineStr">
@@ -4491,7 +4492,7 @@
       </c>
       <c r="J77" s="21" t="inlineStr">
         <is>
-          <t>แจ้งเซลส์ทันทีเมื่อพร้อม / SLA ≤ 4 ชม.</t>
+          <t>แจ้งเซลล์ทันทีเมื่อพร้อม / SLA ≤ 4 ชม.</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4525,7 @@
       <c r="F78" s="19" t="inlineStr">
         <is>
           <t>1) บัญชีออก Invoice
-2) เซลส์ส่งลูกค้า
+2) เซลล์ส่งลูกค้า
 3) ลูกค้าโอน
 4) บัญชี verify เงินเข้า</t>
         </is>
@@ -4536,7 +4537,7 @@
       </c>
       <c r="H78" s="19" t="inlineStr">
         <is>
-          <t>บัญชี + เซลส์</t>
+          <t>บัญชี + เซลล์</t>
         </is>
       </c>
       <c r="I78" s="19" t="inlineStr">
@@ -4976,7 +4977,7 @@
       </c>
       <c r="H86" s="17" t="inlineStr">
         <is>
-          <t>เซลส์ + หัวหน้าติดตั้ง</t>
+          <t>เซลล์ + หัวหน้าติดตั้ง</t>
         </is>
       </c>
       <c r="I86" s="17" t="inlineStr">
@@ -5032,7 +5033,7 @@
       </c>
       <c r="H87" s="21" t="inlineStr">
         <is>
-          <t>ประสานงาน + เซลส์</t>
+          <t>ประสานงาน + เซลล์</t>
         </is>
       </c>
       <c r="I87" s="21" t="inlineStr">
@@ -5074,7 +5075,7 @@
       </c>
       <c r="F88" s="19" t="inlineStr">
         <is>
-          <t>1) คนขับ/เซลส์รวบรวมคืน
+          <t>1) คนขับ/เซลล์รวบรวมคืน
 2) บัญชีออกใหม่
 3) ส่งใหม่ภายใน &lt;7 วัน
 4) บันทึก Root Cause</t>
@@ -5087,7 +5088,7 @@
       </c>
       <c r="H88" s="19" t="inlineStr">
         <is>
-          <t>เซลส์ + แอดมิน</t>
+          <t>เซลล์ + แอดมิน</t>
         </is>
       </c>
       <c r="I88" s="19" t="inlineStr">
@@ -5145,7 +5146,7 @@
       </c>
       <c r="F90" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์รับเรื่อง
+          <t>1) เซลล์รับเรื่อง
 2) เปิด Claim Ticket
 3) Trace กลับ Production (Lot/Serial)
 4) แจ้งทีม Claim</t>
@@ -5158,7 +5159,7 @@
       </c>
       <c r="H90" s="21" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="I90" s="21" t="inlineStr">
@@ -5788,7 +5789,7 @@
       </c>
       <c r="J102" s="21" t="inlineStr">
         <is>
-          <t>เช็คเด้ง = ตามทันที + แจ้งเซลส์ + Hold ลูกค้าชั่วคราว</t>
+          <t>เช็คเด้ง = ตามทันที + แจ้งเซลล์ + Hold ลูกค้าชั่วคราว</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5834,7 @@
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t>บัญชี AR + เซลส์</t>
+          <t>บัญชี AR + เซลล์</t>
         </is>
       </c>
       <c r="I103" s="19" t="inlineStr">
@@ -5843,7 +5844,7 @@
       </c>
       <c r="J103" s="19" t="inlineStr">
         <is>
-          <t>30+ เซลส์ตาม / 60+ ผู้จัดการบัญชีตาม / 90+ CEO + พิจารณากฎหมาย</t>
+          <t>30+ เซลล์ตาม / 60+ ผู้จัดการบัญชีตาม / 90+ CEO + พิจารณากฎหมาย</t>
         </is>
       </c>
     </row>
@@ -5876,7 +5877,7 @@
       <c r="F104" s="17" t="inlineStr">
         <is>
           <t>1) ตั้ง Customer Hold
-2) แจ้งเซลส์ + ผู้บริหาร
+2) แจ้งเซลล์ + ผู้บริหาร
 3) ห้ามเปิด SO ใหม่
 4) เจรจาแผนชำระ</t>
         </is>
@@ -5908,15 +5909,15 @@
           <t>🔴 J. บำรุงรักษาเครื่องจักร + Calibration (Equipment PM &amp; Calibration)</t>
         </is>
       </c>
-      <c r="B105" s="15" t="n"/>
-      <c r="C105" s="15" t="n"/>
-      <c r="D105" s="15" t="n"/>
-      <c r="E105" s="15" t="n"/>
-      <c r="F105" s="15" t="n"/>
-      <c r="G105" s="15" t="n"/>
-      <c r="H105" s="15" t="n"/>
-      <c r="I105" s="15" t="n"/>
-      <c r="J105" s="15" t="n"/>
+      <c r="B105" s="24" t="n"/>
+      <c r="C105" s="24" t="n"/>
+      <c r="D105" s="24" t="n"/>
+      <c r="E105" s="24" t="n"/>
+      <c r="F105" s="24" t="n"/>
+      <c r="G105" s="24" t="n"/>
+      <c r="H105" s="24" t="n"/>
+      <c r="I105" s="24" t="n"/>
+      <c r="J105" s="25" t="n"/>
     </row>
     <row r="106" ht="110" customHeight="1" s="7">
       <c r="A106" s="20" t="inlineStr">
@@ -6261,15 +6262,15 @@
           <t>🔴 K. ความปลอดภัย / 5S / EHS (Safety / 5S / Environment-Health-Safety)</t>
         </is>
       </c>
-      <c r="B112" s="15" t="n"/>
-      <c r="C112" s="15" t="n"/>
-      <c r="D112" s="15" t="n"/>
-      <c r="E112" s="15" t="n"/>
-      <c r="F112" s="15" t="n"/>
-      <c r="G112" s="15" t="n"/>
-      <c r="H112" s="15" t="n"/>
-      <c r="I112" s="15" t="n"/>
-      <c r="J112" s="15" t="n"/>
+      <c r="B112" s="24" t="n"/>
+      <c r="C112" s="24" t="n"/>
+      <c r="D112" s="24" t="n"/>
+      <c r="E112" s="24" t="n"/>
+      <c r="F112" s="24" t="n"/>
+      <c r="G112" s="24" t="n"/>
+      <c r="H112" s="24" t="n"/>
+      <c r="I112" s="24" t="n"/>
+      <c r="J112" s="25" t="n"/>
     </row>
     <row r="113" ht="110" customHeight="1" s="7">
       <c r="A113" s="16" t="inlineStr">
@@ -6614,15 +6615,15 @@
           <t>🔴 L. ฝึกอบรม + Competency Matrix (Training &amp; Competency)</t>
         </is>
       </c>
-      <c r="B119" s="15" t="n"/>
-      <c r="C119" s="15" t="n"/>
-      <c r="D119" s="15" t="n"/>
-      <c r="E119" s="15" t="n"/>
-      <c r="F119" s="15" t="n"/>
-      <c r="G119" s="15" t="n"/>
-      <c r="H119" s="15" t="n"/>
-      <c r="I119" s="15" t="n"/>
-      <c r="J119" s="15" t="n"/>
+      <c r="B119" s="24" t="n"/>
+      <c r="C119" s="24" t="n"/>
+      <c r="D119" s="24" t="n"/>
+      <c r="E119" s="24" t="n"/>
+      <c r="F119" s="24" t="n"/>
+      <c r="G119" s="24" t="n"/>
+      <c r="H119" s="24" t="n"/>
+      <c r="I119" s="24" t="n"/>
+      <c r="J119" s="25" t="n"/>
     </row>
     <row r="120" ht="110" customHeight="1" s="7">
       <c r="A120" s="20" t="inlineStr">
@@ -6910,15 +6911,15 @@
           <t>🔴 N. ควบคุมเอกสาร SOP (Document Control)</t>
         </is>
       </c>
-      <c r="B125" s="15" t="n"/>
-      <c r="C125" s="15" t="n"/>
-      <c r="D125" s="15" t="n"/>
-      <c r="E125" s="15" t="n"/>
-      <c r="F125" s="15" t="n"/>
-      <c r="G125" s="15" t="n"/>
-      <c r="H125" s="15" t="n"/>
-      <c r="I125" s="15" t="n"/>
-      <c r="J125" s="15" t="n"/>
+      <c r="B125" s="24" t="n"/>
+      <c r="C125" s="24" t="n"/>
+      <c r="D125" s="24" t="n"/>
+      <c r="E125" s="24" t="n"/>
+      <c r="F125" s="24" t="n"/>
+      <c r="G125" s="24" t="n"/>
+      <c r="H125" s="24" t="n"/>
+      <c r="I125" s="24" t="n"/>
+      <c r="J125" s="25" t="n"/>
     </row>
     <row r="126" ht="110" customHeight="1" s="7">
       <c r="A126" s="20" t="inlineStr">
@@ -7007,7 +7008,7 @@
           <t>1) Owner draft SOP
 2) ส่ง Reviewer ตรวจ
 3) Approver เซ็นอนุมัติ
-4) อัพเข้า DMS เป็น Version ใหม่
+4) อัปเข้า DMS เป็น Version ใหม่
 5) Lock Version เก่าเป็น Obsolete</t>
         </is>
       </c>
@@ -7205,15 +7206,15 @@
           <t>🟡 O. KPI Dashboard (KPI Tracking &amp; Visualization)</t>
         </is>
       </c>
-      <c r="B131" s="15" t="n"/>
-      <c r="C131" s="15" t="n"/>
-      <c r="D131" s="15" t="n"/>
-      <c r="E131" s="15" t="n"/>
-      <c r="F131" s="15" t="n"/>
-      <c r="G131" s="15" t="n"/>
-      <c r="H131" s="15" t="n"/>
-      <c r="I131" s="15" t="n"/>
-      <c r="J131" s="15" t="n"/>
+      <c r="B131" s="24" t="n"/>
+      <c r="C131" s="24" t="n"/>
+      <c r="D131" s="24" t="n"/>
+      <c r="E131" s="24" t="n"/>
+      <c r="F131" s="24" t="n"/>
+      <c r="G131" s="24" t="n"/>
+      <c r="H131" s="24" t="n"/>
+      <c r="I131" s="24" t="n"/>
+      <c r="J131" s="25" t="n"/>
     </row>
     <row r="132" ht="110" customHeight="1" s="7">
       <c r="A132" s="20" t="inlineStr">
@@ -7501,15 +7502,15 @@
           <t>🟡 P. Internal Audit + Management Review</t>
         </is>
       </c>
-      <c r="B137" s="15" t="n"/>
-      <c r="C137" s="15" t="n"/>
-      <c r="D137" s="15" t="n"/>
-      <c r="E137" s="15" t="n"/>
-      <c r="F137" s="15" t="n"/>
-      <c r="G137" s="15" t="n"/>
-      <c r="H137" s="15" t="n"/>
-      <c r="I137" s="15" t="n"/>
-      <c r="J137" s="15" t="n"/>
+      <c r="B137" s="24" t="n"/>
+      <c r="C137" s="24" t="n"/>
+      <c r="D137" s="24" t="n"/>
+      <c r="E137" s="24" t="n"/>
+      <c r="F137" s="24" t="n"/>
+      <c r="G137" s="24" t="n"/>
+      <c r="H137" s="24" t="n"/>
+      <c r="I137" s="24" t="n"/>
+      <c r="J137" s="25" t="n"/>
     </row>
     <row r="138" ht="110" customHeight="1" s="7">
       <c r="A138" s="20" t="inlineStr">
@@ -7797,15 +7798,15 @@
           <t>🟡 Q. พัฒนา Supplier (Supplier Development Program)</t>
         </is>
       </c>
-      <c r="B143" s="15" t="n"/>
-      <c r="C143" s="15" t="n"/>
-      <c r="D143" s="15" t="n"/>
-      <c r="E143" s="15" t="n"/>
-      <c r="F143" s="15" t="n"/>
-      <c r="G143" s="15" t="n"/>
-      <c r="H143" s="15" t="n"/>
-      <c r="I143" s="15" t="n"/>
-      <c r="J143" s="15" t="n"/>
+      <c r="B143" s="24" t="n"/>
+      <c r="C143" s="24" t="n"/>
+      <c r="D143" s="24" t="n"/>
+      <c r="E143" s="24" t="n"/>
+      <c r="F143" s="24" t="n"/>
+      <c r="G143" s="24" t="n"/>
+      <c r="H143" s="24" t="n"/>
+      <c r="I143" s="24" t="n"/>
+      <c r="J143" s="25" t="n"/>
     </row>
     <row r="144" ht="110" customHeight="1" s="7">
       <c r="A144" s="20" t="inlineStr">
@@ -8093,15 +8094,15 @@
           <t>🟡 R. Forecasting + Sales Planning (S&amp;OP)</t>
         </is>
       </c>
-      <c r="B149" s="15" t="n"/>
-      <c r="C149" s="15" t="n"/>
-      <c r="D149" s="15" t="n"/>
-      <c r="E149" s="15" t="n"/>
-      <c r="F149" s="15" t="n"/>
-      <c r="G149" s="15" t="n"/>
-      <c r="H149" s="15" t="n"/>
-      <c r="I149" s="15" t="n"/>
-      <c r="J149" s="15" t="n"/>
+      <c r="B149" s="24" t="n"/>
+      <c r="C149" s="24" t="n"/>
+      <c r="D149" s="24" t="n"/>
+      <c r="E149" s="24" t="n"/>
+      <c r="F149" s="24" t="n"/>
+      <c r="G149" s="24" t="n"/>
+      <c r="H149" s="24" t="n"/>
+      <c r="I149" s="24" t="n"/>
+      <c r="J149" s="25" t="n"/>
     </row>
     <row r="150" ht="110" customHeight="1" s="7">
       <c r="A150" s="20" t="inlineStr">
@@ -8131,7 +8132,7 @@
       </c>
       <c r="F150" s="21" t="inlineStr">
         <is>
-          <t>1) เซลส์ประมาณการ Pipeline
+          <t>1) เซลล์ประมาณการ Pipeline
 2) บัญชีดูประวัติ
 3) Manager รวมและปรับ
 4) ส่งเข้า S&amp;OP
@@ -8145,7 +8146,7 @@
       </c>
       <c r="H150" s="21" t="inlineStr">
         <is>
-          <t>เซลส์ + ผู้จัดการขาย</t>
+          <t>เซลล์ + ผู้จัดการขาย</t>
         </is>
       </c>
       <c r="I150" s="21" t="inlineStr">
@@ -8358,7 +8359,7 @@
           <t>1) คำนวณ Accuracy รายเดือน
 2) วิเคราะห์ Bias (สูงเกิน/ต่ำเกิน)
 3) ปรับวิธี Forecast
-4) Train เซลส์ที่ Accuracy ต่ำ
+4) Train เซลล์ที่ Accuracy ต่ำ
 5) ทบทวนรายไตรมาส</t>
         </is>
       </c>
@@ -8379,7 +8380,7 @@
       </c>
       <c r="J154" s="21" t="inlineStr">
         <is>
-          <t>Target Accuracy ≥ 70% / ใช้คุมโบนัสเซลส์</t>
+          <t>Target Accuracy ≥ 70% / ใช้คุมโบนัสเซลล์</t>
         </is>
       </c>
     </row>
@@ -8389,15 +8390,15 @@
           <t>🟡 S. Warranty Management (จัดการการรับประกัน)</t>
         </is>
       </c>
-      <c r="B155" s="15" t="n"/>
-      <c r="C155" s="15" t="n"/>
-      <c r="D155" s="15" t="n"/>
-      <c r="E155" s="15" t="n"/>
-      <c r="F155" s="15" t="n"/>
-      <c r="G155" s="15" t="n"/>
-      <c r="H155" s="15" t="n"/>
-      <c r="I155" s="15" t="n"/>
-      <c r="J155" s="15" t="n"/>
+      <c r="B155" s="24" t="n"/>
+      <c r="C155" s="24" t="n"/>
+      <c r="D155" s="24" t="n"/>
+      <c r="E155" s="24" t="n"/>
+      <c r="F155" s="24" t="n"/>
+      <c r="G155" s="24" t="n"/>
+      <c r="H155" s="24" t="n"/>
+      <c r="I155" s="24" t="n"/>
+      <c r="J155" s="25" t="n"/>
     </row>
     <row r="156" ht="110" customHeight="1" s="7">
       <c r="A156" s="20" t="inlineStr">
@@ -8685,15 +8686,15 @@
           <t>🟢 T. Continuous Improvement / Kaizen (ปรับปรุงต่อเนื่อง)</t>
         </is>
       </c>
-      <c r="B161" s="15" t="n"/>
-      <c r="C161" s="15" t="n"/>
-      <c r="D161" s="15" t="n"/>
-      <c r="E161" s="15" t="n"/>
-      <c r="F161" s="15" t="n"/>
-      <c r="G161" s="15" t="n"/>
-      <c r="H161" s="15" t="n"/>
-      <c r="I161" s="15" t="n"/>
-      <c r="J161" s="15" t="n"/>
+      <c r="B161" s="24" t="n"/>
+      <c r="C161" s="24" t="n"/>
+      <c r="D161" s="24" t="n"/>
+      <c r="E161" s="24" t="n"/>
+      <c r="F161" s="24" t="n"/>
+      <c r="G161" s="24" t="n"/>
+      <c r="H161" s="24" t="n"/>
+      <c r="I161" s="24" t="n"/>
+      <c r="J161" s="25" t="n"/>
     </row>
     <row r="162" ht="110" customHeight="1" s="7">
       <c r="A162" s="20" t="inlineStr">
@@ -8980,15 +8981,15 @@
           <t>🟢 U. HR + Payroll Integration (เชื่อมข้อมูลคนกับเงินเดือน)</t>
         </is>
       </c>
-      <c r="B167" s="15" t="n"/>
-      <c r="C167" s="15" t="n"/>
-      <c r="D167" s="15" t="n"/>
-      <c r="E167" s="15" t="n"/>
-      <c r="F167" s="15" t="n"/>
-      <c r="G167" s="15" t="n"/>
-      <c r="H167" s="15" t="n"/>
-      <c r="I167" s="15" t="n"/>
-      <c r="J167" s="15" t="n"/>
+      <c r="B167" s="24" t="n"/>
+      <c r="C167" s="24" t="n"/>
+      <c r="D167" s="24" t="n"/>
+      <c r="E167" s="24" t="n"/>
+      <c r="F167" s="24" t="n"/>
+      <c r="G167" s="24" t="n"/>
+      <c r="H167" s="24" t="n"/>
+      <c r="I167" s="24" t="n"/>
+      <c r="J167" s="25" t="n"/>
     </row>
     <row r="168" ht="110" customHeight="1" s="7">
       <c r="A168" s="20" t="inlineStr">
@@ -9276,15 +9277,15 @@
           <t>🟢 V. IT Backup + BCP (สำรองข้อมูล + แผนฉุกเฉิน IT)</t>
         </is>
       </c>
-      <c r="B173" s="15" t="n"/>
-      <c r="C173" s="15" t="n"/>
-      <c r="D173" s="15" t="n"/>
-      <c r="E173" s="15" t="n"/>
-      <c r="F173" s="15" t="n"/>
-      <c r="G173" s="15" t="n"/>
-      <c r="H173" s="15" t="n"/>
-      <c r="I173" s="15" t="n"/>
-      <c r="J173" s="15" t="n"/>
+      <c r="B173" s="24" t="n"/>
+      <c r="C173" s="24" t="n"/>
+      <c r="D173" s="24" t="n"/>
+      <c r="E173" s="24" t="n"/>
+      <c r="F173" s="24" t="n"/>
+      <c r="G173" s="24" t="n"/>
+      <c r="H173" s="24" t="n"/>
+      <c r="I173" s="24" t="n"/>
+      <c r="J173" s="25" t="n"/>
     </row>
     <row r="174" ht="110" customHeight="1" s="7">
       <c r="A174" s="16" t="inlineStr">
@@ -9572,15 +9573,15 @@
           <t>🟢 W. Risk Register (ทะเบียนความเสี่ยง)</t>
         </is>
       </c>
-      <c r="B179" s="15" t="n"/>
-      <c r="C179" s="15" t="n"/>
-      <c r="D179" s="15" t="n"/>
-      <c r="E179" s="15" t="n"/>
-      <c r="F179" s="15" t="n"/>
-      <c r="G179" s="15" t="n"/>
-      <c r="H179" s="15" t="n"/>
-      <c r="I179" s="15" t="n"/>
-      <c r="J179" s="15" t="n"/>
+      <c r="B179" s="24" t="n"/>
+      <c r="C179" s="24" t="n"/>
+      <c r="D179" s="24" t="n"/>
+      <c r="E179" s="24" t="n"/>
+      <c r="F179" s="24" t="n"/>
+      <c r="G179" s="24" t="n"/>
+      <c r="H179" s="24" t="n"/>
+      <c r="I179" s="24" t="n"/>
+      <c r="J179" s="25" t="n"/>
     </row>
     <row r="180" ht="110" customHeight="1" s="7">
       <c r="A180" s="20" t="inlineStr">
@@ -9928,6 +9929,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="24" customHeight="1" s="7">
       <c r="A4" s="1" t="inlineStr">
         <is>
@@ -10024,12 +10026,12 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -10081,7 +10083,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
@@ -10124,7 +10126,7 @@
       <c r="E8" s="3" t="inlineStr">
         <is>
           <t>ผ่านการตรวจ(A2)
-เซลส์ + จัดซื้อ</t>
+เซลล์ + จัดซื้อ</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -10228,7 +10230,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -10238,7 +10240,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
@@ -10296,7 +10298,7 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -10306,7 +10308,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
@@ -10403,7 +10405,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>ฝ่ายแบบ + เซลส์ + ผลิต</t>
+          <t>ฝ่ายแบบ + เซลล์ + ผลิต</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
@@ -10413,7 +10415,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>ฝ่ายแบบ + เซลส์ + ผลิต</t>
+          <t>ฝ่ายแบบ + เซลล์ + ผลิต</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
@@ -10428,7 +10430,7 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>เซลส์ต้องร่วมฟังเสมอ / โครงการใหญ่ต้อง Kick-off Meeting
+          <t>เซลล์ต้องร่วมฟังเสมอ / โครงการใหญ่ต้อง Kick-off Meeting
 ฝ่ายแบบคุยกับลูกค้าเองได้ แต่ต้องให้ Sales ร่วมฟังและออกความคิดเห็นรับข้อยอมร่วมกันทั้ง 3 ฝ่าย</t>
         </is>
       </c>
@@ -10456,7 +10458,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -10466,7 +10468,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
@@ -10508,7 +10510,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>ลูกค้า / เซลส์ / ผลิต</t>
+          <t>ลูกค้า / เซลล์ / ผลิต</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -10523,7 +10525,7 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>หัวหน้าแบบ / เซลส์ / ลูกค้า</t>
+          <t>หัวหน้าแบบ / เซลล์ / ลูกค้า</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -10533,7 +10535,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>ฟรี 3 รอบ / เกินคิดค่าใช้จ่าย / เซลส์ BOM-ต้นทุน กำหนดส่งทุกครั้ง</t>
+          <t>ฟรี 3 รอบ / เกินคิดค่าใช้จ่าย / เซลล์ BOM-ต้นทุน กำหนดส่งทุกครั้ง</t>
         </is>
       </c>
     </row>
@@ -10561,8 +10563,8 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>ลูกค้า / เซลส์
-เซลส์ / แอดมินขาย</t>
+          <t>ลูกค้า / เซลล์
+เซลล์ / แอดมินขาย</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
@@ -10614,7 +10616,7 @@
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>เซลส์
+          <t>เซลล์
 หรือผู้มีอำนาจในเรื่องขอส่งด่วน</t>
         </is>
       </c>
@@ -10669,7 +10671,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
@@ -10722,7 +10724,7 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
@@ -10786,12 +10788,12 @@
       <c r="D22" s="3" t="inlineStr">
         <is>
           <t>แบบอนุมัติฉบับสมบูรณ์ + PO
-+ แผนการรับสินค้าจากเซลส์</t>
++ แผนการรับสินค้าจากเซลล์</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -10943,7 +10945,7 @@
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>รายการที่ต้องซื้อ +
-แผนการรับสินค้าจากเซลส์</t>
+แผนการรับสินค้าจากเซลล์</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -11055,7 +11057,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>จัดซื้อ + เซลส์ + ฝ่ายผลิต</t>
+          <t>จัดซื้อ + เซลล์ + ฝ่ายผลิต</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -11070,7 +11072,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>หัวหน้า Planner + เซลส์</t>
+          <t>หัวหน้า Planner + เซลล์</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -11569,7 +11571,7 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
@@ -11589,7 +11591,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>แจ้งเซลส์ทันทีเมื่อพร้อม</t>
+          <t>แจ้งเซลล์ทันทีเมื่อพร้อม</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11623,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -11673,7 +11675,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>เซลส์ / ลูกค้า</t>
+          <t>เซลล์ / ลูกค้า</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -11829,12 +11831,12 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>เซลส์ / คนขับ</t>
+          <t>เซลล์ / คนขับ</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
@@ -11945,12 +11947,12 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
@@ -11992,7 +11994,7 @@
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
@@ -12309,12 +12311,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -12366,7 +12368,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H4" s="5" t="inlineStr">
@@ -12409,7 +12411,7 @@
       <c r="E5" s="3" t="inlineStr">
         <is>
           <t>ผ่านการตรวจ(A2)
-เซลส์ + จัดซื้อ</t>
+เซลล์ + จัดซื้อ</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -12513,7 +12515,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -12523,7 +12525,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
@@ -12661,7 +12663,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -12671,7 +12673,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -12768,7 +12770,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ฝ่ายแบบ + เซลส์ + ผลิต</t>
+          <t>ฝ่ายแบบ + เซลล์ + ผลิต</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -12778,7 +12780,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ฝ่ายแบบ + เซลส์ + ผลิต</t>
+          <t>ฝ่ายแบบ + เซลล์ + ผลิต</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -12793,7 +12795,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>เซลส์ต้องร่วมฟังเสมอ / โครงการใหญ่ต้อง Kick-off Meeting
+          <t>เซลล์ต้องร่วมฟังเสมอ / โครงการใหญ่ต้อง Kick-off Meeting
 ฝ่ายแบบคุยกับลูกค้าเองได้ แต่ต้องให้ Sales ร่วมฟังและออกความคิดเห็นรับข้อยอมร่วมกันทั้ง 3 ฝ่าย</t>
         </is>
       </c>
@@ -12821,7 +12823,7 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -12831,7 +12833,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -12873,7 +12875,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>ลูกค้า / เซลส์ / ผลิต</t>
+          <t>ลูกค้า / เซลล์ / ผลิต</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -12888,7 +12890,7 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>หัวหน้าแบบ / เซลส์ / ลูกค้า</t>
+          <t>หัวหน้าแบบ / เซลล์ / ลูกค้า</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -12898,7 +12900,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>ฟรี 3 รอบ / เกินคิดค่าใช้จ่าย / เซลส์ BOM-ต้นทุน กำหนดส่งทุกครั้ง</t>
+          <t>ฟรี 3 รอบ / เกินคิดค่าใช้จ่าย / เซลล์ BOM-ต้นทุน กำหนดส่งทุกครั้ง</t>
         </is>
       </c>
     </row>
@@ -12926,8 +12928,8 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>ลูกค้า / เซลส์
-เซลส์ / แอดมินขาย</t>
+          <t>ลูกค้า / เซลล์
+เซลล์ / แอดมินขาย</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -12979,7 +12981,7 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>เซลส์
+          <t>เซลล์
 หรือผู้มีอำนาจในเรื่องขอส่งด่วน</t>
         </is>
       </c>
@@ -13034,7 +13036,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -13087,7 +13089,7 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -13231,12 +13233,12 @@
       <c r="D3" s="3" t="inlineStr">
         <is>
           <t>แบบอนุมัติฉบับสมบูรณ์ + PO
-+ แผนการรับสินค้าจากเซลส์</t>
++ แผนการรับสินค้าจากเซลล์</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -13388,7 +13390,7 @@
       <c r="D6" s="5" t="inlineStr">
         <is>
           <t>รายการที่ต้องซื้อ +
-แผนการรับสินค้าจากเซลส์</t>
+แผนการรับสินค้าจากเซลล์</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -13500,7 +13502,7 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>จัดซื้อ + เซลส์ + ฝ่ายผลิต</t>
+          <t>จัดซื้อ + เซลล์ + ฝ่ายผลิต</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -13515,7 +13517,7 @@
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>หัวหน้า Planner + เซลส์</t>
+          <t>หัวหน้า Planner + เซลล์</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -14254,7 +14256,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -14274,7 +14276,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>แจ้งเซลส์ทันทีเมื่อพร้อม</t>
+          <t>แจ้งเซลล์ทันทีเมื่อพร้อม</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14308,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -14358,7 +14360,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>เซลส์ / ลูกค้า</t>
+          <t>เซลล์ / ลูกค้า</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -14514,12 +14516,12 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>เซลส์ / คนขับ</t>
+          <t>เซลล์ / คนขับ</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
@@ -14710,12 +14712,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -14757,7 +14759,7 @@
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>เซลส์</t>
+          <t>เซลล์</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
